--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_UNO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_UNO.xlsx
@@ -3362,11 +3362,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="27276565"/>
-        <c:axId val="87232732"/>
+        <c:axId val="47434526"/>
+        <c:axId val="20953686"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="27276565"/>
+        <c:axId val="47434526"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3400,7 +3400,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87232732"/>
+        <c:crossAx val="20953686"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3412,7 +3412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="87232732"/>
+        <c:axId val="20953686"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3455,7 +3455,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27276565"/>
+        <c:crossAx val="47434526"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4986,11 +4986,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="30481277"/>
-        <c:axId val="29519173"/>
+        <c:axId val="50986274"/>
+        <c:axId val="4233133"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="30481277"/>
+        <c:axId val="50986274"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5022,7 +5022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29519173"/>
+        <c:crossAx val="4233133"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5033,7 +5033,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="29519173"/>
+        <c:axId val="4233133"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5109,7 +5109,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30481277"/>
+        <c:crossAx val="50986274"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7486,11 +7486,11 @@
       </c>
       <c r="AH9" s="25" t="n">
         <f aca="false">+S11/R11-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AQ9" s="16" t="n">
         <f aca="false">+(S11/P11-1)/COUNTA(AE9:AP9)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AR9" s="9"/>
       <c r="AS9" s="9"/>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="S11" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U11" s="19"/>
       <c r="Y11" s="19"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="AW21" s="34" t="n">
         <f aca="false">LOOKUP(AW20,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX21" s="34" t="n">
         <f aca="false">LOOKUP(AX20,$A$3:$A$2972,$B$3:$B$2972)</f>
@@ -9582,23 +9582,23 @@
       </c>
       <c r="AX30" s="44" t="n">
         <f aca="false">$AW21/AX21-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY30" s="44" t="n">
         <f aca="false">$AW21/AY21-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ30" s="44" t="n">
         <f aca="false">$AW21/AZ21-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA30" s="44" t="n">
         <f aca="false">$AW21/BA21-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB30" s="44" t="n">
         <f aca="false">+AQ57</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC30" s="45"/>
       <c r="BD30" s="38"/>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="AH57" s="55" t="n">
         <f aca="false">+AH9</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI57" s="55"/>
       <c r="AJ57" s="55"/>
@@ -11842,7 +11842,7 @@
       <c r="AP57" s="55"/>
       <c r="AQ57" s="55" t="n">
         <f aca="false">+AQ9</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AS57" s="9"/>
     </row>
@@ -17848,15 +17848,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="24" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>103.310747989011</v>
+        <v>104.791905166963</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -17982,23 +17982,23 @@
       </c>
       <c r="T2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!AX30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!AY30</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ30</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!BA30</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!BB30</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="H26" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!AH57</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I26" s="79"/>
       <c r="J26" s="79"/>
@@ -19325,7 +19325,7 @@
       <c r="P26" s="79"/>
       <c r="Q26" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ57</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_UNO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_UNO.xlsx
@@ -3362,11 +3362,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47434526"/>
-        <c:axId val="20953686"/>
+        <c:axId val="32318347"/>
+        <c:axId val="80559414"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="47434526"/>
+        <c:axId val="32318347"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3400,7 +3400,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20953686"/>
+        <c:crossAx val="80559414"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3412,7 +3412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="20953686"/>
+        <c:axId val="80559414"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3455,7 +3455,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47434526"/>
+        <c:crossAx val="32318347"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4986,11 +4986,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="50986274"/>
-        <c:axId val="4233133"/>
+        <c:axId val="87463249"/>
+        <c:axId val="8789542"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="50986274"/>
+        <c:axId val="87463249"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5022,7 +5022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4233133"/>
+        <c:crossAx val="8789542"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5033,7 +5033,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="4233133"/>
+        <c:axId val="8789542"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5109,7 +5109,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50986274"/>
+        <c:crossAx val="87463249"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_UNO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_UNO.xlsx
@@ -3362,11 +3362,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="32318347"/>
-        <c:axId val="80559414"/>
+        <c:axId val="40197704"/>
+        <c:axId val="16727477"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="32318347"/>
+        <c:axId val="40197704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3400,7 +3400,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80559414"/>
+        <c:crossAx val="16727477"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3412,7 +3412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80559414"/>
+        <c:axId val="16727477"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3455,7 +3455,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32318347"/>
+        <c:crossAx val="40197704"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4986,11 +4986,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="87463249"/>
-        <c:axId val="8789542"/>
+        <c:axId val="40082811"/>
+        <c:axId val="58659102"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="87463249"/>
+        <c:axId val="40082811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5022,7 +5022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8789542"/>
+        <c:crossAx val="58659102"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5033,7 +5033,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="8789542"/>
+        <c:axId val="58659102"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5109,7 +5109,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87463249"/>
+        <c:crossAx val="40082811"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_UNO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_UNO.xlsx
@@ -3362,11 +3362,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40197704"/>
-        <c:axId val="16727477"/>
+        <c:axId val="68885984"/>
+        <c:axId val="63524702"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="40197704"/>
+        <c:axId val="68885984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3400,7 +3400,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16727477"/>
+        <c:crossAx val="63524702"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3412,7 +3412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="16727477"/>
+        <c:axId val="63524702"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3455,7 +3455,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40197704"/>
+        <c:crossAx val="68885984"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4986,11 +4986,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="40082811"/>
-        <c:axId val="58659102"/>
+        <c:axId val="9239487"/>
+        <c:axId val="36481938"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="40082811"/>
+        <c:axId val="9239487"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5022,7 +5022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58659102"/>
+        <c:crossAx val="36481938"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5033,7 +5033,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="58659102"/>
+        <c:axId val="36481938"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5109,7 +5109,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40082811"/>
+        <c:crossAx val="9239487"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
